--- a/data/trans_orig/P64D$andando_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según cómo se desplaza desde su casa al centro de trabajo/estudios, mediante, al menos, una de las opciones (multirrespuesta) en 2023</t>
+          <t>Población según cómo se desplaza desde su casa al centro de trabajo/estudios, mediante, al menos, una de las opciones (multirrespuesta) en 2023 (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68869</t>
+          <t>68657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101143</t>
+          <t>99352</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86439</t>
+          <t>85713</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111537</t>
+          <t>111911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161236</t>
+          <t>160470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203453</t>
+          <t>202768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,62 +878,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4346</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>5228</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>256650</t>
+          <t>258646</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>285619</t>
+          <t>286438</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>156292</t>
+          <t>154829</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>180296</t>
+          <t>181607</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>419829</t>
+          <t>421118</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>460771</t>
+          <t>462166</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>12217</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19835</t>
+          <t>20360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>17700</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19763</t>
+          <t>19312</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30806</t>
+          <t>32477</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53616</t>
+          <t>54381</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191471</t>
+          <t>191360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149328</t>
+          <t>149613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183435</t>
+          <t>183037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155829</t>
+          <t>154747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>381140</t>
+          <t>376675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2450</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>13809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>607854</t>
+          <t>605249</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>752896</t>
+          <t>750893</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>241320</t>
+          <t>242903</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>274538</t>
+          <t>276202</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>852247</t>
+          <t>853704</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1055500</t>
+          <t>1059696</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>11624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52007</t>
+          <t>52849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39676</t>
+          <t>38171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29644</t>
+          <t>32316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84145</t>
+          <t>83817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33181</t>
+          <t>35411</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>45705</t>
+          <t>44906</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44481</t>
+          <t>43312</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76910</t>
+          <t>76077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52174</t>
+          <t>50319</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90760</t>
+          <t>90080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105494</t>
+          <t>106257</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152547</t>
+          <t>155026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>270595</t>
+          <t>269471</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>303874</t>
+          <t>304652</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>230015</t>
+          <t>229628</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>267936</t>
+          <t>269768</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>510579</t>
+          <t>510845</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>561309</t>
+          <t>560856</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28935</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>18528</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40490</t>
+          <t>40906</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34013</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62547</t>
+          <t>62877</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>18172</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28417</t>
+          <t>27575</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99708</t>
+          <t>100520</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>138795</t>
+          <t>139329</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99450</t>
+          <t>100089</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>193829</t>
+          <t>193361</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>212090</t>
+          <t>216012</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>313394</t>
+          <t>312164</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>8665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27081</t>
+          <t>29102</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>219321</t>
+          <t>244099</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19628</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>321935</t>
+          <t>287688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>273594</t>
+          <t>269987</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>315479</t>
+          <t>314941</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>128270</t>
+          <t>119159</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>244584</t>
+          <t>245855</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>362243</t>
+          <t>381739</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>550196</t>
+          <t>550466</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57498</t>
+          <t>57282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>89661</t>
+          <t>90433</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52730</t>
+          <t>51697</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107945</t>
+          <t>109223</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>123551</t>
+          <t>121470</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>184770</t>
+          <t>183683</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>331</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>51634</t>
+          <t>53098</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>31091</t>
+          <t>32612</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>43318</t>
+          <t>41874</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>77553</t>
+          <t>77272</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>256105</t>
+          <t>255714</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>453789</t>
+          <t>451392</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>418556</t>
+          <t>423386</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>546259</t>
+          <t>541374</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>676360</t>
+          <t>691675</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>977176</t>
+          <t>977130</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37416</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>301237</t>
+          <t>299486</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31321</t>
+          <t>31386</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>398185</t>
+          <t>377216</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1457763</t>
+          <t>1453831</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1673040</t>
+          <t>1670403</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>738808</t>
+          <t>735063</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>939288</t>
+          <t>936876</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2249815</t>
+          <t>2257817</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2625071</t>
+          <t>2597394</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>83786</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>158391</t>
+          <t>158237</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>122483</t>
+          <t>119889</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>177543</t>
+          <t>174491</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>213515</t>
+          <t>217072</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>319655</t>
+          <t>317880</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27537</t>
+          <t>27774</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>16711</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15689</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>37855</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>48465</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>97633</t>
+          <t>99132</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>38912</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>66157</t>
+          <t>66794</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>96243</t>
+          <t>95297</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>151993</t>
+          <t>152098</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">

--- a/data/trans_orig/P64D$andando_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>82865</t>
+          <t>92665</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68657</t>
+          <t>75497</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99352</t>
+          <t>112228</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>98537</t>
+          <t>104007</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85713</t>
+          <t>90630</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111911</t>
+          <t>118904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>181402</t>
+          <t>196671</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160470</t>
+          <t>175595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>202768</t>
+          <t>218400</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>273113</t>
+          <t>292985</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>258646</t>
+          <t>275379</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>286438</t>
+          <t>308280</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>169098</t>
+          <t>184039</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>154829</t>
+          <t>169825</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>181607</t>
+          <t>196642</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>442210</t>
+          <t>477025</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>421118</t>
+          <t>455646</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>462166</t>
+          <t>498358</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20360</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>634</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>23008</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19312</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>26392</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14772</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32477</t>
+          <t>37909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>126273</t>
+          <t>152437</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54381</t>
+          <t>128597</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191360</t>
+          <t>176463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>165895</t>
+          <t>186734</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149613</t>
+          <t>167398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183037</t>
+          <t>206454</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>292167</t>
+          <t>339171</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154747</t>
+          <t>308108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>376675</t>
+          <t>371407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>674916</t>
+          <t>469058</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>605249</t>
+          <t>444208</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>750893</t>
+          <t>493286</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>260185</t>
+          <t>283608</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>242903</t>
+          <t>262646</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>276202</t>
+          <t>300842</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>935100</t>
+          <t>752666</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>853704</t>
+          <t>718434</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1059696</t>
+          <t>783643</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>72,89%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32111</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>29128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52849</t>
+          <t>58505</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>35454</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20076</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>46955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>61313</t>
+          <t>76751</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32316</t>
+          <t>60632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83817</t>
+          <t>95482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17687</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>21443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35411</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>21293</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>32241</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>44906</t>
+          <t>46682</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>57121</t>
+          <t>63425</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43312</t>
+          <t>47220</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76077</t>
+          <t>81903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>73743</t>
+          <t>91558</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50319</t>
+          <t>77564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90080</t>
+          <t>108206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>130864</t>
+          <t>154983</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106257</t>
+          <t>133198</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155026</t>
+          <t>176661</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>27171</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>11018</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>35837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>288774</t>
+          <t>335750</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>269471</t>
+          <t>313168</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>304652</t>
+          <t>353029</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>246432</t>
+          <t>240123</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>229628</t>
+          <t>225247</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>269768</t>
+          <t>255936</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>535206</t>
+          <t>575872</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>510845</t>
+          <t>548156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>560856</t>
+          <t>599767</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>36260</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>34851</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18528</t>
+          <t>25156</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40906</t>
+          <t>45922</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>45594</t>
+          <t>57651</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32397</t>
+          <t>43777</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62877</t>
+          <t>75811</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12958</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2654,67 +2654,67 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>8867</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>15623</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>7994</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>21818</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>32739</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>117756</t>
+          <t>130799</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100520</t>
+          <t>110646</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139329</t>
+          <t>153145</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>159753</t>
+          <t>172630</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100089</t>
+          <t>153820</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>193361</t>
+          <t>189477</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>277509</t>
+          <t>303429</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216012</t>
+          <t>278547</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>312164</t>
+          <t>331950</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>14764</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>29015</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>76199</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>244099</t>
+          <t>16190</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>90963</t>
+          <t>27351</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>287688</t>
+          <t>40326</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>294522</t>
+          <t>310213</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>269987</t>
+          <t>284853</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>314941</t>
+          <t>333434</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>204095</t>
+          <t>212679</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>119159</t>
+          <t>194859</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>245855</t>
+          <t>231408</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>498617</t>
+          <t>522892</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>381739</t>
+          <t>495064</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>550466</t>
+          <t>553310</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,37%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>72163</t>
+          <t>87289</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57282</t>
+          <t>70067</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90433</t>
+          <t>109084</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>85121</t>
+          <t>95018</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51697</t>
+          <t>78366</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>109223</t>
+          <t>111709</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>157284</t>
+          <t>182307</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>121470</t>
+          <t>159332</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>183683</t>
+          <t>207288</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>23118</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>37708</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26536</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>53098</t>
+          <t>60961</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>32612</t>
+          <t>34918</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>68401</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>41874</t>
+          <t>53761</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>77272</t>
+          <t>86486</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>384014</t>
+          <t>439326</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>255714</t>
+          <t>398335</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>451392</t>
+          <t>480334</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>497928</t>
+          <t>554929</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>423386</t>
+          <t>521053</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>541374</t>
+          <t>587603</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>881942</t>
+          <t>994255</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>691675</t>
+          <t>940498</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>977130</t>
+          <t>1043525</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>24970</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15077</t>
+          <t>24122</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>299486</t>
+          <t>24974</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>55245</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31386</t>
+          <t>40842</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>377216</t>
+          <t>76760</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1531325</t>
+          <t>1408006</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1453831</t>
+          <t>1363077</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1670403</t>
+          <t>1449760</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>879809</t>
+          <t>920448</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>735063</t>
+          <t>884410</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>936876</t>
+          <t>953875</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2411135</t>
+          <t>2328455</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2257817</t>
+          <t>2271399</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2597394</t>
+          <t>2384275</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>127982</t>
+          <t>158560</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>80741</t>
+          <t>132684</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>158237</t>
+          <t>189371</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>148643</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>119889</t>
+          <t>149700</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>174491</t>
+          <t>195560</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>276625</t>
+          <t>331335</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>217072</t>
+          <t>294712</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>317880</t>
+          <t>366744</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16711</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>23200</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>48465</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>99132</t>
+          <t>108552</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>40003</t>
+          <t>49386</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>66794</t>
+          <t>77749</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>125623</t>
+          <t>148852</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>95297</t>
+          <t>126351</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>152098</t>
+          <t>177170</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
           <t>3,67%</t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P64D$andando_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Habitat-trans_orig.xlsx
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>292985</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>275379</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>308280</t>
+          <t>23008</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>184039</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>169825</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>196642</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>477025</t>
+          <t>26392</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>455646</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>498358</t>
+          <t>37909</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1054,112 +1054,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>634</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12767</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22215</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1167,112 +1167,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>271</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>292985</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>275379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>308280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>266</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>184039</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>169825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>196642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>537</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>477025</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>455646</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>498358</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -1280,112 +1280,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23008</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21756</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>26392</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37909</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -1623,112 +1623,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>469058</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>444208</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>493286</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>283608</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>262646</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>300842</t>
+          <t>21293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>752666</t>
+          <t>32241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>718434</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>783643</t>
+          <t>46682</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1736,112 +1736,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41297</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29128</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58505</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35454</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46955</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>76751</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60632</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95482</t>
+          <t>21443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1849,112 +1849,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>401</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>469058</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>444208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>493286</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>388</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>283608</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>262646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>300842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>789</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12119</t>
+          <t>752666</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>718434</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21443</t>
+          <t>783643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>72,89%</t>
         </is>
       </c>
     </row>
@@ -1962,112 +1962,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9291</t>
+          <t>29128</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30327</t>
+          <t>58505</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14329</t>
+          <t>35454</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>46955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>77</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>32241</t>
+          <t>76751</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21918</t>
+          <t>60632</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>46682</t>
+          <t>95482</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -2305,112 +2305,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>335750</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>313168</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>353029</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>240123</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>225247</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>255936</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>575872</t>
+          <t>21818</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>548156</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>599767</t>
+          <t>32739</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2418,112 +2418,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22800</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34851</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45922</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>57651</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43777</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75811</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2531,112 +2531,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>266</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>335750</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>313168</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>353029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>304</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>240123</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>225247</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>255936</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>570</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>575872</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>548156</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>599767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -2644,112 +2644,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>36260</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>34851</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>25156</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>45922</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>21818</t>
+          <t>57651</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>43777</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32739</t>
+          <t>75811</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -2987,112 +2987,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>310213</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>284853</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>333434</t>
+          <t>60961</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>212679</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>194859</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>231408</t>
+          <t>34918</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>69</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>522892</t>
+          <t>68401</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>495064</t>
+          <t>53761</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>553310</t>
+          <t>86486</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -3100,112 +3100,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>87289</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70067</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109084</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>95018</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78366</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111709</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>182307</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>159332</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>207288</t>
+          <t>23118</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -3213,112 +3213,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>297</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>310213</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>284853</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10674</t>
+          <t>333434</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>299</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>212679</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>194859</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>231408</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>596</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>522892</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>495064</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23118</t>
+          <t>553310</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>57,37%</t>
         </is>
       </c>
     </row>
@@ -3326,112 +3326,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>87289</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>70067</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60961</t>
+          <t>109084</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>95018</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>78366</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>34918</t>
+          <t>111709</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>190</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>68401</t>
+          <t>182307</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>53761</t>
+          <t>159332</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>86486</t>
+          <t>207288</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -3669,112 +3669,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1408006</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1363077</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1449760</t>
+          <t>108552</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>920448</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>884410</t>
+          <t>49386</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>953875</t>
+          <t>77749</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>152</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2328455</t>
+          <t>148852</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2271399</t>
+          <t>126351</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2384275</t>
+          <t>177170</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -3782,112 +3782,112 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>158560</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>132684</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>189371</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>172774</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>149700</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>195560</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>331335</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>294712</t>
+          <t>23200</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>366744</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3895,112 +3895,112 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>21439</t>
+          <t>1408006</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>1363077</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>33169</t>
+          <t>1449760</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>920448</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>884410</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>953875</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>34384</t>
+          <t>2328455</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>2271399</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>48742</t>
+          <t>2384275</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -4008,112 +4008,112 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>132</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>86023</t>
+          <t>158560</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>67045</t>
+          <t>132684</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>108552</t>
+          <t>189371</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>208</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>62829</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>49386</t>
+          <t>149700</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>77749</t>
+          <t>195560</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>340</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>148852</t>
+          <t>331335</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>126351</t>
+          <t>294712</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>177170</t>
+          <t>366744</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
